--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123303396</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123305277</v>
+        <v>123307047</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -861,17 +861,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343369</v>
+        <v>343295</v>
       </c>
       <c r="R3" t="n">
-        <v>6523829</v>
+        <v>6523704</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,11 +901,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123307047</v>
+        <v>123305277</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,17 +987,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343295</v>
+        <v>343369</v>
       </c>
       <c r="R4" t="n">
-        <v>6523704</v>
+        <v>6523829</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,6 +1027,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123303396</v>
+        <v>123307047</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343545</v>
+        <v>343295</v>
       </c>
       <c r="R2" t="n">
-        <v>6523658</v>
+        <v>6523704</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123307047</v>
+        <v>123303396</v>
       </c>
       <c r="B3" t="n">
         <v>57851</v>
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343295</v>
+        <v>343545</v>
       </c>
       <c r="R3" t="n">
-        <v>6523704</v>
+        <v>6523658</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,6 +896,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123307047</v>
+        <v>123303396</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343295</v>
+        <v>343545</v>
       </c>
       <c r="R2" t="n">
-        <v>6523704</v>
+        <v>6523658</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +770,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303396</v>
+        <v>123305277</v>
       </c>
       <c r="B3" t="n">
         <v>57851</v>
@@ -856,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343545</v>
+        <v>343369</v>
       </c>
       <c r="R3" t="n">
-        <v>6523658</v>
+        <v>6523829</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -900,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123305277</v>
+        <v>123307047</v>
       </c>
       <c r="B4" t="n">
         <v>57851</v>
@@ -987,17 +992,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343369</v>
+        <v>343295</v>
       </c>
       <c r="R4" t="n">
-        <v>6523829</v>
+        <v>6523704</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,11 +1032,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123303396</v>
+        <v>123305277</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343545</v>
+        <v>343369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523658</v>
+        <v>6523829</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123305277</v>
+        <v>123303396</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343369</v>
+        <v>343545</v>
       </c>
       <c r="R3" t="n">
-        <v>6523829</v>
+        <v>6523658</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,7 +940,7 @@
         <v>123307047</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123305277</v>
+        <v>123303396</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343369</v>
+        <v>343545</v>
       </c>
       <c r="R2" t="n">
-        <v>6523829</v>
+        <v>6523658</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303396</v>
+        <v>123307047</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343545</v>
+        <v>343295</v>
       </c>
       <c r="R3" t="n">
-        <v>6523658</v>
+        <v>6523704</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,11 +901,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123307047</v>
+        <v>123305277</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,17 +987,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343295</v>
+        <v>343369</v>
       </c>
       <c r="R4" t="n">
-        <v>6523704</v>
+        <v>6523829</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,6 +1027,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123303396</v>
+        <v>123305277</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -730,14 +730,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343545</v>
+        <v>343369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523658</v>
+        <v>6523829</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,7 +809,7 @@
         <v>123307047</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123305277</v>
+        <v>123303396</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343369</v>
+        <v>343545</v>
       </c>
       <c r="R4" t="n">
-        <v>6523829</v>
+        <v>6523658</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123305277</v>
+        <v>123307047</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343369</v>
+        <v>343295</v>
       </c>
       <c r="R2" t="n">
-        <v>6523829</v>
+        <v>6523704</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123307047</v>
+        <v>123303396</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343295</v>
+        <v>343545</v>
       </c>
       <c r="R3" t="n">
-        <v>6523704</v>
+        <v>6523658</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,6 +896,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123303396</v>
+        <v>123305277</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343545</v>
+        <v>343369</v>
       </c>
       <c r="R4" t="n">
-        <v>6523658</v>
+        <v>6523829</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303396</v>
+        <v>123305277</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -856,14 +856,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343545</v>
+        <v>343369</v>
       </c>
       <c r="R3" t="n">
-        <v>6523658</v>
+        <v>6523829</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123305277</v>
+        <v>123303396</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343369</v>
+        <v>343545</v>
       </c>
       <c r="R4" t="n">
-        <v>6523829</v>
+        <v>6523658</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123307047</v>
+        <v>123305277</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandkasen, Sandkasen, Dls</t>
+          <t>Gårmyrarna, Gårmyrarna, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343295</v>
+        <v>343369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523704</v>
+        <v>6523829</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,6 +770,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123305277</v>
+        <v>123303396</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -856,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårmyrarna, Gårmyrarna, Dls</t>
+          <t>Sandkasen, Sandkasen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343369</v>
+        <v>343545</v>
       </c>
       <c r="R3" t="n">
-        <v>6523829</v>
+        <v>6523658</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -900,7 +905,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I äldre flerskiktad granskog.</t>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123303396</v>
+        <v>123307047</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -991,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343545</v>
+        <v>343295</v>
       </c>
       <c r="R4" t="n">
-        <v>6523658</v>
+        <v>6523704</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,11 +1032,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8305-2025 artfynd.xlsx
+++ b/artfynd/A 8305-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123303396</v>
+        <v>123307047</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343545</v>
+        <v>343295</v>
       </c>
       <c r="R3" t="n">
-        <v>6523658</v>
+        <v>6523704</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,11 +901,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123307047</v>
+        <v>123303396</v>
       </c>
       <c r="B4" t="n">
         <v>57861</v>
@@ -996,13 +991,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343295</v>
+        <v>343545</v>
       </c>
       <c r="R4" t="n">
-        <v>6523704</v>
+        <v>6523658</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,6 +1027,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I gammal delvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
